--- a/jogos_2026-05-16.xlsx
+++ b/jogos_2026-05-16.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.45</v>
+        <v>2.77</v>
       </c>
       <c r="Q75" t="n">
-        <v>5.95</v>
+        <v>4.41</v>
       </c>
       <c r="R75" t="n">
-        <v>6.36</v>
+        <v>2.34</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.28</v>
+        <v>1.45</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.31</v>
+        <v>5.95</v>
       </c>
       <c r="R76" t="n">
-        <v>2.09</v>
+        <v>6.36</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.82</v>
+        <v>2.57</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.1</v>
+        <v>4.22</v>
       </c>
       <c r="R77" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.77</v>
+        <v>3.7</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.41</v>
+        <v>4.52</v>
       </c>
       <c r="R78" t="n">
-        <v>2.34</v>
+        <v>1.91</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.52</v>
+        <v>4.31</v>
       </c>
       <c r="R80" t="n">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.57</v>
+        <v>1.28</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.22</v>
+        <v>7.13</v>
       </c>
       <c r="R82" t="n">
-        <v>2.57</v>
+        <v>11</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.28</v>
+        <v>2.77</v>
       </c>
       <c r="Q83" t="n">
-        <v>7.13</v>
+        <v>3.49</v>
       </c>
       <c r="R83" t="n">
-        <v>11</v>
+        <v>2.72</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.77</v>
+        <v>3.48</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.49</v>
+        <v>4.19</v>
       </c>
       <c r="R84" t="n">
-        <v>2.72</v>
+        <v>2.05</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17358,124 +17358,124 @@
         <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AJ86" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK86" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL86" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM86" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AN86" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO86" t="n">
         <v>0</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR86" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AS86" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AT86" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AU86" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AV86" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW86" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX86" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY86" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ86" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BA86" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BB86" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC86" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD86" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE86" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF86" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17752,124 +17752,124 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V88" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W88" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI88" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK88" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL88" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM88" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AN88" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO88" t="n">
         <v>0</v>
       </c>
       <c r="AP88" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR88" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS88" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AU88" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AV88" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW88" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX88" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY88" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ88" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA88" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BB88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC88" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD88" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE88" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF88" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R111" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,22 +27742,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,22 +32076,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32120,7 +32120,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P161" t="n">
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32317,7 +32317,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,22 +33258,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,22 +33455,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,22 +34834,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="Q187" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="R187" t="n">
-        <v>4.32</v>
+        <v>3.83</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="R188" t="n">
-        <v>3.83</v>
+        <v>4.32</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q200" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R200" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40201,13 +40201,13 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q202" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R202" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S202" t="n">
         <v>0</v>
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,22 +41532,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,22 +41729,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,22 +41926,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44881,22 +44881,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,22 +45275,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,22 +46457,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q234" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46550,10 +46550,10 @@
         <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF234" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG234" t="n">
         <v>0</v>
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49609,22 +49609,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,22 +50003,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50051,13 +50051,13 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q252" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R252" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="S252" t="n">
         <v>0</v>
@@ -50096,10 +50096,10 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF252" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG252" t="n">
         <v>0</v>
@@ -50200,22 +50200,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,22 +50397,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G259" t="n">

--- a/jogos_2026-05-16.xlsx
+++ b/jogos_2026-05-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI265"/>
+  <dimension ref="A1:BI269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.36</v>
+        <v>4.67</v>
       </c>
       <c r="Q21" t="n">
         <v>3.46</v>
       </c>
       <c r="R21" t="n">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46158.33333333334</v>
+        <v>46158.29166666666</v>
       </c>
     </row>
     <row r="26">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46158.34375</v>
+        <v>46158.33333333334</v>
       </c>
     </row>
     <row r="29">
@@ -6067,27 +6067,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46158.35416666666</v>
+        <v>46158.33333333334</v>
       </c>
     </row>
     <row r="30">
@@ -6264,27 +6264,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46158.35416666666</v>
+        <v>46158.34375</v>
       </c>
     </row>
     <row r="31">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9219,27 +9219,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46158.35763888889</v>
+        <v>46158.35416666666</v>
       </c>
     </row>
     <row r="46">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>46158.36458333334</v>
+        <v>46158.35416666666</v>
       </c>
     </row>
     <row r="47">
@@ -9613,27 +9613,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46158.375</v>
+        <v>46158.35763888889</v>
       </c>
     </row>
     <row r="48">
@@ -9810,12 +9810,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46158.375</v>
+        <v>46158.36458333334</v>
       </c>
     </row>
     <row r="49">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="BI60" s="3" t="n">
-        <v>46158.40625</v>
+        <v>46158.375</v>
       </c>
     </row>
     <row r="61">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>46158.41666666666</v>
+        <v>46158.375</v>
       </c>
     </row>
     <row r="62">
@@ -12568,27 +12568,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>46158.41666666666</v>
+        <v>46158.375</v>
       </c>
     </row>
     <row r="63">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12953,7 +12953,7 @@
         <v>0</v>
       </c>
       <c r="BI63" s="3" t="n">
-        <v>46158.41666666666</v>
+        <v>46158.40625</v>
       </c>
     </row>
     <row r="64">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15129,27 +15129,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>46158.4375</v>
+        <v>46158.41666666666</v>
       </c>
     </row>
     <row r="76">
@@ -15326,12 +15326,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15514,7 +15514,7 @@
         <v>0</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>46158.4375</v>
+        <v>46158.41666666666</v>
       </c>
     </row>
     <row r="77">
@@ -15523,12 +15523,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>46158.4375</v>
+        <v>46158.41666666666</v>
       </c>
     </row>
     <row r="78">
@@ -15720,12 +15720,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15908,7 +15908,7 @@
         <v>0</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>46158.4375</v>
+        <v>46158.41666666666</v>
       </c>
     </row>
     <row r="79">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.82</v>
+        <v>3.48</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.1</v>
+        <v>4.19</v>
       </c>
       <c r="R79" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.77</v>
+        <v>3.7</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.49</v>
+        <v>4.52</v>
       </c>
       <c r="R83" t="n">
-        <v>2.72</v>
+        <v>1.91</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>3.48</v>
+        <v>2.77</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.19</v>
+        <v>3.49</v>
       </c>
       <c r="R84" t="n">
-        <v>2.05</v>
+        <v>2.72</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17099,27 +17099,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>46158.45833333334</v>
+        <v>46158.4375</v>
       </c>
     </row>
     <row r="86">
@@ -17296,27 +17296,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17484,7 +17484,7 @@
         <v>0</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>46158.45833333334</v>
+        <v>46158.4375</v>
       </c>
     </row>
     <row r="87">
@@ -17493,27 +17493,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17681,7 +17681,7 @@
         <v>0</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>46158.45833333334</v>
+        <v>46158.4375</v>
       </c>
     </row>
     <row r="88">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17752,124 +17752,124 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI88" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AJ88" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK88" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL88" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM88" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AN88" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO88" t="n">
         <v>0</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR88" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AS88" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AT88" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AU88" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AV88" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW88" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX88" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY88" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ88" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BA88" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BB88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC88" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD88" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE88" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF88" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20313,124 +20313,124 @@
         <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U101" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V101" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W101" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG101" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AH101" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI101" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AJ101" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK101" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL101" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM101" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AN101" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO101" t="n">
         <v>0</v>
       </c>
       <c r="AP101" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR101" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS101" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AU101" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AV101" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW101" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX101" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY101" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ101" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA101" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BB101" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC101" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD101" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE101" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF101" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG101" t="n">
         <v>0</v>
@@ -20439,7 +20439,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3" t="n">
-        <v>46158.46875</v>
+        <v>46158.45833333334</v>
       </c>
     </row>
     <row r="102">
@@ -20448,27 +20448,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20636,7 +20636,7 @@
         <v>0</v>
       </c>
       <c r="BI102" s="3" t="n">
-        <v>46158.46875</v>
+        <v>46158.45833333334</v>
       </c>
     </row>
     <row r="103">
@@ -20645,27 +20645,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20833,7 +20833,7 @@
         <v>0</v>
       </c>
       <c r="BI103" s="3" t="n">
-        <v>46158.5</v>
+        <v>46158.45833333334</v>
       </c>
     </row>
     <row r="104">
@@ -20842,12 +20842,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21030,7 +21030,7 @@
         <v>0</v>
       </c>
       <c r="BI104" s="3" t="n">
-        <v>46158.5</v>
+        <v>46158.46875</v>
       </c>
     </row>
     <row r="105">
@@ -21039,12 +21039,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21227,7 +21227,7 @@
         <v>0</v>
       </c>
       <c r="BI105" s="3" t="n">
-        <v>46158.5</v>
+        <v>46158.46875</v>
       </c>
     </row>
     <row r="106">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="Q111" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R111" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R119" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24782,12 +24782,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24970,7 +24970,7 @@
         <v>0</v>
       </c>
       <c r="BI124" s="3" t="n">
-        <v>46158.51041666666</v>
+        <v>46158.5</v>
       </c>
     </row>
     <row r="125">
@@ -24979,12 +24979,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25167,7 +25167,7 @@
         <v>0</v>
       </c>
       <c r="BI125" s="3" t="n">
-        <v>46158.51041666666</v>
+        <v>46158.5</v>
       </c>
     </row>
     <row r="126">
@@ -25176,12 +25176,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25364,7 +25364,7 @@
         <v>0</v>
       </c>
       <c r="BI126" s="3" t="n">
-        <v>46158.51041666666</v>
+        <v>46158.5</v>
       </c>
     </row>
     <row r="127">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25570,12 +25570,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25758,7 +25758,7 @@
         <v>0</v>
       </c>
       <c r="BI128" s="3" t="n">
-        <v>46158.52083333334</v>
+        <v>46158.51041666666</v>
       </c>
     </row>
     <row r="129">
@@ -25767,12 +25767,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25955,7 +25955,7 @@
         <v>0</v>
       </c>
       <c r="BI129" s="3" t="n">
-        <v>46158.52083333334</v>
+        <v>46158.51041666666</v>
       </c>
     </row>
     <row r="130">
@@ -25964,12 +25964,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26152,7 +26152,7 @@
         <v>0</v>
       </c>
       <c r="BI130" s="3" t="n">
-        <v>46158.52083333334</v>
+        <v>46158.51041666666</v>
       </c>
     </row>
     <row r="131">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27343,12 +27343,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27531,7 +27531,7 @@
         <v>0</v>
       </c>
       <c r="BI137" s="3" t="n">
-        <v>46158.54166666666</v>
+        <v>46158.52083333334</v>
       </c>
     </row>
     <row r="138">
@@ -27540,12 +27540,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27728,7 +27728,7 @@
         <v>0</v>
       </c>
       <c r="BI138" s="3" t="n">
-        <v>46158.54166666666</v>
+        <v>46158.52083333334</v>
       </c>
     </row>
     <row r="139">
@@ -27737,27 +27737,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27925,7 +27925,7 @@
         <v>0</v>
       </c>
       <c r="BI139" s="3" t="n">
-        <v>46158.54166666666</v>
+        <v>46158.52083333334</v>
       </c>
     </row>
     <row r="140">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30298,12 +30298,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30486,7 +30486,7 @@
         <v>0</v>
       </c>
       <c r="BI152" s="3" t="n">
-        <v>46158.54513888889</v>
+        <v>46158.54166666666</v>
       </c>
     </row>
     <row r="153">
@@ -30495,12 +30495,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30683,7 +30683,7 @@
         <v>0</v>
       </c>
       <c r="BI153" s="3" t="n">
-        <v>46158.54513888889</v>
+        <v>46158.54166666666</v>
       </c>
     </row>
     <row r="154">
@@ -30692,12 +30692,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30880,7 +30880,7 @@
         <v>0</v>
       </c>
       <c r="BI154" s="3" t="n">
-        <v>46158.55208333334</v>
+        <v>46158.54166666666</v>
       </c>
     </row>
     <row r="155">
@@ -30889,12 +30889,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31077,7 +31077,7 @@
         <v>0</v>
       </c>
       <c r="BI155" s="3" t="n">
-        <v>46158.55208333334</v>
+        <v>46158.54513888889</v>
       </c>
     </row>
     <row r="156">
@@ -31086,12 +31086,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31274,7 +31274,7 @@
         <v>0</v>
       </c>
       <c r="BI156" s="3" t="n">
-        <v>46158.5625</v>
+        <v>46158.54513888889</v>
       </c>
     </row>
     <row r="157">
@@ -31283,12 +31283,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31471,7 +31471,7 @@
         <v>0</v>
       </c>
       <c r="BI157" s="3" t="n">
-        <v>46158.5625</v>
+        <v>46158.55208333334</v>
       </c>
     </row>
     <row r="158">
@@ -31480,12 +31480,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31668,7 +31668,7 @@
         <v>0</v>
       </c>
       <c r="BI158" s="3" t="n">
-        <v>46158.5625</v>
+        <v>46158.55208333334</v>
       </c>
     </row>
     <row r="159">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32071,12 +32071,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32120,7 +32120,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P161" t="n">
@@ -32259,7 +32259,7 @@
         <v>0</v>
       </c>
       <c r="BI161" s="3" t="n">
-        <v>46158.58333333334</v>
+        <v>46158.5625</v>
       </c>
     </row>
     <row r="162">
@@ -32268,27 +32268,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32456,7 +32456,7 @@
         <v>0</v>
       </c>
       <c r="BI162" s="3" t="n">
-        <v>46158.58333333334</v>
+        <v>46158.5625</v>
       </c>
     </row>
     <row r="163">
@@ -32465,27 +32465,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32653,7 +32653,7 @@
         <v>0</v>
       </c>
       <c r="BI163" s="3" t="n">
-        <v>46158.60416666666</v>
+        <v>46158.5625</v>
       </c>
     </row>
     <row r="164">
@@ -32662,12 +32662,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -32677,12 +32677,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32711,7 +32711,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -32850,7 +32850,7 @@
         <v>0</v>
       </c>
       <c r="BI164" s="3" t="n">
-        <v>46158.60416666666</v>
+        <v>46158.58333333334</v>
       </c>
     </row>
     <row r="165">
@@ -32859,27 +32859,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33047,7 +33047,7 @@
         <v>0</v>
       </c>
       <c r="BI165" s="3" t="n">
-        <v>46158.60416666666</v>
+        <v>46158.58333333334</v>
       </c>
     </row>
     <row r="166">
@@ -33253,12 +33253,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33441,7 +33441,7 @@
         <v>0</v>
       </c>
       <c r="BI167" s="3" t="n">
-        <v>46158.625</v>
+        <v>46158.60416666666</v>
       </c>
     </row>
     <row r="168">
@@ -33450,27 +33450,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33638,7 +33638,7 @@
         <v>0</v>
       </c>
       <c r="BI168" s="3" t="n">
-        <v>46158.625</v>
+        <v>46158.60416666666</v>
       </c>
     </row>
     <row r="169">
@@ -33647,12 +33647,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33835,7 +33835,7 @@
         <v>0</v>
       </c>
       <c r="BI169" s="3" t="n">
-        <v>46158.63541666666</v>
+        <v>46158.60416666666</v>
       </c>
     </row>
     <row r="170">
@@ -33844,12 +33844,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34032,7 +34032,7 @@
         <v>0</v>
       </c>
       <c r="BI170" s="3" t="n">
-        <v>46158.63541666666</v>
+        <v>46158.625</v>
       </c>
     </row>
     <row r="171">
@@ -34041,7 +34041,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34229,7 +34229,7 @@
         <v>0</v>
       </c>
       <c r="BI171" s="3" t="n">
-        <v>46158.64583333334</v>
+        <v>46158.625</v>
       </c>
     </row>
     <row r="172">
@@ -34238,12 +34238,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34426,7 +34426,7 @@
         <v>0</v>
       </c>
       <c r="BI172" s="3" t="n">
-        <v>46158.64583333334</v>
+        <v>46158.625</v>
       </c>
     </row>
     <row r="173">
@@ -34435,12 +34435,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34623,7 +34623,7 @@
         <v>0</v>
       </c>
       <c r="BI173" s="3" t="n">
-        <v>46158.64583333334</v>
+        <v>46158.625</v>
       </c>
     </row>
     <row r="174">
@@ -34632,27 +34632,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34820,7 +34820,7 @@
         <v>0</v>
       </c>
       <c r="BI174" s="3" t="n">
-        <v>46158.65625</v>
+        <v>46158.63541666666</v>
       </c>
     </row>
     <row r="175">
@@ -34829,12 +34829,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35017,7 +35017,7 @@
         <v>0</v>
       </c>
       <c r="BI175" s="3" t="n">
-        <v>46158.65625</v>
+        <v>46158.63541666666</v>
       </c>
     </row>
     <row r="176">
@@ -35026,7 +35026,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35214,7 +35214,7 @@
         <v>0</v>
       </c>
       <c r="BI176" s="3" t="n">
-        <v>46158.66666666666</v>
+        <v>46158.64583333334</v>
       </c>
     </row>
     <row r="177">
@@ -35223,12 +35223,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35411,7 +35411,7 @@
         <v>0</v>
       </c>
       <c r="BI177" s="3" t="n">
-        <v>46158.66666666666</v>
+        <v>46158.64583333334</v>
       </c>
     </row>
     <row r="178">
@@ -35420,12 +35420,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35608,7 +35608,7 @@
         <v>0</v>
       </c>
       <c r="BI178" s="3" t="n">
-        <v>46158.66666666666</v>
+        <v>46158.65625</v>
       </c>
     </row>
     <row r="179">
@@ -35617,27 +35617,27 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35805,7 +35805,7 @@
         <v>0</v>
       </c>
       <c r="BI179" s="3" t="n">
-        <v>46158.66666666666</v>
+        <v>46158.65625</v>
       </c>
     </row>
     <row r="180">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36602,12 +36602,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36790,7 +36790,7 @@
         <v>0</v>
       </c>
       <c r="BI184" s="3" t="n">
-        <v>46158.72916666666</v>
+        <v>46158.66666666666</v>
       </c>
     </row>
     <row r="185">
@@ -36799,7 +36799,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36987,7 +36987,7 @@
         <v>0</v>
       </c>
       <c r="BI185" s="3" t="n">
-        <v>46158.76041666666</v>
+        <v>46158.66666666666</v>
       </c>
     </row>
     <row r="186">
@@ -36996,12 +36996,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37184,7 +37184,7 @@
         <v>0</v>
       </c>
       <c r="BI186" s="3" t="n">
-        <v>46158.77083333334</v>
+        <v>46158.66666666666</v>
       </c>
     </row>
     <row r="187">
@@ -37193,12 +37193,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37381,7 +37381,7 @@
         <v>0</v>
       </c>
       <c r="BI187" s="3" t="n">
-        <v>46158.77083333334</v>
+        <v>46158.66666666666</v>
       </c>
     </row>
     <row r="188">
@@ -37390,12 +37390,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37578,7 +37578,7 @@
         <v>0</v>
       </c>
       <c r="BI188" s="3" t="n">
-        <v>46158.77083333334</v>
+        <v>46158.72916666666</v>
       </c>
     </row>
     <row r="189">
@@ -37587,12 +37587,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="BI189" s="3" t="n">
-        <v>46158.77083333334</v>
+        <v>46158.76041666666</v>
       </c>
     </row>
     <row r="190">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q190" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R190" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -38178,12 +38178,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q192" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38366,7 +38366,7 @@
         <v>0</v>
       </c>
       <c r="BI192" s="3" t="n">
-        <v>46158.79166666666</v>
+        <v>46158.77083333334</v>
       </c>
     </row>
     <row r="193">
@@ -38375,12 +38375,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38563,7 +38563,7 @@
         <v>0</v>
       </c>
       <c r="BI193" s="3" t="n">
-        <v>46158.79166666666</v>
+        <v>46158.77083333334</v>
       </c>
     </row>
     <row r="194">
@@ -38572,12 +38572,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38760,7 +38760,7 @@
         <v>0</v>
       </c>
       <c r="BI194" s="3" t="n">
-        <v>46158.8125</v>
+        <v>46158.77083333334</v>
       </c>
     </row>
     <row r="195">
@@ -38769,12 +38769,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38957,7 +38957,7 @@
         <v>0</v>
       </c>
       <c r="BI195" s="3" t="n">
-        <v>46158.85416666666</v>
+        <v>46158.77083333334</v>
       </c>
     </row>
     <row r="196">
@@ -38966,12 +38966,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39154,7 +39154,7 @@
         <v>0</v>
       </c>
       <c r="BI196" s="3" t="n">
-        <v>46158.85416666666</v>
+        <v>46158.79166666666</v>
       </c>
     </row>
     <row r="197">
@@ -39163,12 +39163,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39351,7 +39351,7 @@
         <v>0</v>
       </c>
       <c r="BI197" s="3" t="n">
-        <v>46158.85416666666</v>
+        <v>46158.79166666666</v>
       </c>
     </row>
     <row r="198">
@@ -39360,12 +39360,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39548,7 +39548,7 @@
         <v>0</v>
       </c>
       <c r="BI198" s="3" t="n">
-        <v>46158.85416666666</v>
+        <v>46158.8125</v>
       </c>
     </row>
     <row r="199">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q200" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R200" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40542,27 +40542,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q204" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R204" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40730,7 +40730,7 @@
         <v>0</v>
       </c>
       <c r="BI204" s="3" t="n">
-        <v>46158.875</v>
+        <v>46158.85416666666</v>
       </c>
     </row>
     <row r="205">
@@ -40739,27 +40739,27 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40927,7 +40927,7 @@
         <v>0</v>
       </c>
       <c r="BI205" s="3" t="n">
-        <v>46158.875</v>
+        <v>46158.85416666666</v>
       </c>
     </row>
     <row r="206">
@@ -40936,27 +40936,27 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41124,7 +41124,7 @@
         <v>0</v>
       </c>
       <c r="BI206" s="3" t="n">
-        <v>46158.875</v>
+        <v>46158.85416666666</v>
       </c>
     </row>
     <row r="207">
@@ -41133,27 +41133,27 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41321,7 +41321,7 @@
         <v>0</v>
       </c>
       <c r="BI207" s="3" t="n">
-        <v>46158.875</v>
+        <v>46158.85416666666</v>
       </c>
     </row>
     <row r="208">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,22 +41926,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,22 +44290,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44881,22 +44881,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,22 +47442,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47490,13 +47490,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q239" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R239" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -47535,10 +47535,10 @@
         <v>0</v>
       </c>
       <c r="AE239" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF239" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG239" t="n">
         <v>0</v>
@@ -47639,22 +47639,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49609,22 +49609,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,22 +50003,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50051,13 +50051,13 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q252" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="S252" t="n">
         <v>0</v>
@@ -50096,10 +50096,10 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF252" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG252" t="n">
         <v>0</v>
@@ -50200,22 +50200,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,22 +50397,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50983,27 +50983,27 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51171,7 +51171,7 @@
         <v>0</v>
       </c>
       <c r="BI257" s="3" t="n">
-        <v>46158.89583333334</v>
+        <v>46158.875</v>
       </c>
     </row>
     <row r="258">
@@ -51180,27 +51180,27 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51368,7 +51368,7 @@
         <v>0</v>
       </c>
       <c r="BI258" s="3" t="n">
-        <v>46158.89583333334</v>
+        <v>46158.875</v>
       </c>
     </row>
     <row r="259">
@@ -51377,27 +51377,27 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51565,7 +51565,7 @@
         <v>0</v>
       </c>
       <c r="BI259" s="3" t="n">
-        <v>46158.89583333334</v>
+        <v>46158.875</v>
       </c>
     </row>
     <row r="260">
@@ -51574,27 +51574,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51762,7 +51762,7 @@
         <v>0</v>
       </c>
       <c r="BI260" s="3" t="n">
-        <v>46158.90625</v>
+        <v>46158.875</v>
       </c>
     </row>
     <row r="261">
@@ -51771,7 +51771,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51959,7 +51959,7 @@
         <v>0</v>
       </c>
       <c r="BI261" s="3" t="n">
-        <v>46158.91666666666</v>
+        <v>46158.89583333334</v>
       </c>
     </row>
     <row r="262">
@@ -51968,12 +51968,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52156,7 +52156,7 @@
         <v>0</v>
       </c>
       <c r="BI262" s="3" t="n">
-        <v>46158.9375</v>
+        <v>46158.89583333334</v>
       </c>
     </row>
     <row r="263">
@@ -52165,7 +52165,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52353,7 +52353,7 @@
         <v>0</v>
       </c>
       <c r="BI263" s="3" t="n">
-        <v>46158.9375</v>
+        <v>46158.89583333334</v>
       </c>
     </row>
     <row r="264">
@@ -52362,12 +52362,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52550,7 +52550,7 @@
         <v>0</v>
       </c>
       <c r="BI264" s="3" t="n">
-        <v>46158.95833333334</v>
+        <v>46158.90625</v>
       </c>
     </row>
     <row r="265">
@@ -52559,7 +52559,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -52574,12 +52574,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52747,6 +52747,794 @@
         <v>0</v>
       </c>
       <c r="BI265" s="3" t="n">
+        <v>46158.92708333334</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="n">
+        <v>0</v>
+      </c>
+      <c r="L266" t="n">
+        <v>0</v>
+      </c>
+      <c r="M266" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N266" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>0</v>
+      </c>
+      <c r="R266" t="n">
+        <v>0</v>
+      </c>
+      <c r="S266" t="n">
+        <v>0</v>
+      </c>
+      <c r="T266" t="n">
+        <v>0</v>
+      </c>
+      <c r="U266" t="n">
+        <v>0</v>
+      </c>
+      <c r="V266" t="n">
+        <v>0</v>
+      </c>
+      <c r="W266" t="n">
+        <v>0</v>
+      </c>
+      <c r="X266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ266" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA266" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB266" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC266" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD266" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE266" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF266" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG266" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH266" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI266" s="3" t="n">
+        <v>46158.9375</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0</v>
+      </c>
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="n">
+        <v>0</v>
+      </c>
+      <c r="L267" t="n">
+        <v>0</v>
+      </c>
+      <c r="M267" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N267" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>0</v>
+      </c>
+      <c r="R267" t="n">
+        <v>0</v>
+      </c>
+      <c r="S267" t="n">
+        <v>0</v>
+      </c>
+      <c r="T267" t="n">
+        <v>0</v>
+      </c>
+      <c r="U267" t="n">
+        <v>0</v>
+      </c>
+      <c r="V267" t="n">
+        <v>0</v>
+      </c>
+      <c r="W267" t="n">
+        <v>0</v>
+      </c>
+      <c r="X267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ267" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA267" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB267" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC267" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD267" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE267" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF267" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG267" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH267" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI267" s="3" t="n">
+        <v>46158.9375</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Los Angeles II</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>LA Galaxy II</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>0</v>
+      </c>
+      <c r="H268" t="n">
+        <v>0</v>
+      </c>
+      <c r="I268" t="n">
+        <v>0</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="n">
+        <v>0</v>
+      </c>
+      <c r="L268" t="n">
+        <v>0</v>
+      </c>
+      <c r="M268" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N268" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>0</v>
+      </c>
+      <c r="R268" t="n">
+        <v>0</v>
+      </c>
+      <c r="S268" t="n">
+        <v>0</v>
+      </c>
+      <c r="T268" t="n">
+        <v>0</v>
+      </c>
+      <c r="U268" t="n">
+        <v>0</v>
+      </c>
+      <c r="V268" t="n">
+        <v>0</v>
+      </c>
+      <c r="W268" t="n">
+        <v>0</v>
+      </c>
+      <c r="X268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ268" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA268" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB268" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC268" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD268" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE268" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF268" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG268" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH268" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI268" s="3" t="n">
+        <v>46158.95833333334</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" t="n">
+        <v>0</v>
+      </c>
+      <c r="I269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" t="n">
+        <v>0</v>
+      </c>
+      <c r="L269" t="n">
+        <v>0</v>
+      </c>
+      <c r="M269" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N269" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>0</v>
+      </c>
+      <c r="R269" t="n">
+        <v>0</v>
+      </c>
+      <c r="S269" t="n">
+        <v>0</v>
+      </c>
+      <c r="T269" t="n">
+        <v>0</v>
+      </c>
+      <c r="U269" t="n">
+        <v>0</v>
+      </c>
+      <c r="V269" t="n">
+        <v>0</v>
+      </c>
+      <c r="W269" t="n">
+        <v>0</v>
+      </c>
+      <c r="X269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ269" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA269" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB269" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC269" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD269" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE269" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF269" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG269" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH269" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI269" s="3" t="n">
         <v>46158.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-05-16.xlsx
+++ b/jogos_2026-05-16.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.48</v>
+        <v>2.77</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.19</v>
+        <v>3.49</v>
       </c>
       <c r="R79" t="n">
-        <v>2.05</v>
+        <v>2.72</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.28</v>
+        <v>1.28</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.31</v>
+        <v>7.13</v>
       </c>
       <c r="R80" t="n">
-        <v>2.09</v>
+        <v>11</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.82</v>
+        <v>3.28</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.1</v>
+        <v>4.31</v>
       </c>
       <c r="R81" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.28</v>
+        <v>2.82</v>
       </c>
       <c r="Q82" t="n">
-        <v>7.13</v>
+        <v>4.1</v>
       </c>
       <c r="R82" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>3.7</v>
+        <v>1.45</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.52</v>
+        <v>5.95</v>
       </c>
       <c r="R83" t="n">
-        <v>1.91</v>
+        <v>6.36</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16958,10 +16958,10 @@
         <v>2.77</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.49</v>
+        <v>4.41</v>
       </c>
       <c r="R84" t="n">
-        <v>2.72</v>
+        <v>2.34</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.45</v>
+        <v>2.57</v>
       </c>
       <c r="Q85" t="n">
-        <v>5.95</v>
+        <v>4.22</v>
       </c>
       <c r="R85" t="n">
-        <v>6.36</v>
+        <v>2.57</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.77</v>
+        <v>3.48</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.41</v>
+        <v>4.19</v>
       </c>
       <c r="R86" t="n">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.57</v>
+        <v>3.7</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.22</v>
+        <v>4.52</v>
       </c>
       <c r="R87" t="n">
-        <v>2.57</v>
+        <v>1.91</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19722,124 +19722,124 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V98" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG98" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AH98" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI98" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK98" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL98" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM98" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AN98" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO98" t="n">
         <v>0</v>
       </c>
       <c r="AP98" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR98" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS98" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AU98" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AV98" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW98" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX98" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY98" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ98" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA98" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BB98" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD98" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE98" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF98" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG98" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20313,124 +20313,124 @@
         <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U101" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AH101" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI101" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AJ101" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK101" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL101" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM101" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AN101" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO101" t="n">
         <v>0</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR101" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AS101" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AT101" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AU101" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AV101" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW101" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX101" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY101" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ101" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BA101" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BB101" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC101" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD101" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE101" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF101" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,22 +33849,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q190" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q193" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R193" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q204" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R204" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q206" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R206" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,22 +41926,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,22 +43305,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,22 +44290,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,22 +45275,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,22 +45472,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45520,13 +45520,13 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q229" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R229" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -45565,10 +45565,10 @@
         <v>0</v>
       </c>
       <c r="AE229" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF229" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG229" t="n">
         <v>0</v>
@@ -45669,22 +45669,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,22 +46063,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,22 +47442,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47490,13 +47490,13 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q239" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R239" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -47535,10 +47535,10 @@
         <v>0</v>
       </c>
       <c r="AE239" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF239" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG239" t="n">
         <v>0</v>
@@ -47639,22 +47639,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G263" t="n">

--- a/jogos_2026-05-16.xlsx
+++ b/jogos_2026-05-16.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.36</v>
+        <v>4.67</v>
       </c>
       <c r="Q17" t="n">
         <v>3.46</v>
       </c>
       <c r="R17" t="n">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.57</v>
+        <v>3.7</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.22</v>
+        <v>4.52</v>
       </c>
       <c r="R85" t="n">
-        <v>2.57</v>
+        <v>1.91</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.7</v>
+        <v>2.57</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.52</v>
+        <v>4.22</v>
       </c>
       <c r="R87" t="n">
-        <v>1.91</v>
+        <v>2.57</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17752,124 +17752,124 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V88" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W88" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI88" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK88" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL88" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM88" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AN88" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO88" t="n">
         <v>0</v>
       </c>
       <c r="AP88" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR88" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS88" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AU88" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AV88" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW88" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX88" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY88" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ88" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA88" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BB88" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC88" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD88" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE88" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF88" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19722,124 +19722,124 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U98" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V98" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AH98" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI98" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AJ98" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK98" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL98" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM98" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AN98" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO98" t="n">
         <v>0</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR98" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AS98" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AT98" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AU98" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AV98" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW98" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX98" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY98" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ98" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BA98" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BB98" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC98" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD98" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE98" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF98" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,22 +32667,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32711,7 +32711,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -32864,22 +32864,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32908,7 +32908,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q190" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R190" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q193" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q205" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q206" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,22 +42123,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q212" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF212" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,22 +43108,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,22 +43305,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,22 +44290,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,22 +45275,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,22 +45472,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45520,13 +45520,13 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q229" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -45565,10 +45565,10 @@
         <v>0</v>
       </c>
       <c r="AE229" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF229" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG229" t="n">
         <v>0</v>
@@ -45669,22 +45669,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,22 +46063,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49412,22 +49412,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G263" t="n">

--- a/jogos_2026-05-16.xlsx
+++ b/jogos_2026-05-16.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.67</v>
+        <v>3.36</v>
       </c>
       <c r="Q17" t="n">
         <v>3.46</v>
       </c>
       <c r="R17" t="n">
-        <v>1.84</v>
+        <v>2.18</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.49</v>
+        <v>4.31</v>
       </c>
       <c r="R79" t="n">
-        <v>2.72</v>
+        <v>2.09</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.28</v>
+        <v>3.48</v>
       </c>
       <c r="Q80" t="n">
-        <v>7.13</v>
+        <v>4.19</v>
       </c>
       <c r="R80" t="n">
-        <v>11</v>
+        <v>2.05</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.31</v>
+        <v>4.52</v>
       </c>
       <c r="R81" t="n">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.1</v>
+        <v>4.41</v>
       </c>
       <c r="R82" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.41</v>
+        <v>4.1</v>
       </c>
       <c r="R84" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>3.7</v>
+        <v>1.28</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.52</v>
+        <v>7.13</v>
       </c>
       <c r="R85" t="n">
-        <v>1.91</v>
+        <v>11</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>3.48</v>
+        <v>2.77</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.19</v>
+        <v>3.49</v>
       </c>
       <c r="R86" t="n">
-        <v>2.05</v>
+        <v>2.72</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17752,124 +17752,124 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI88" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AJ88" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK88" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL88" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM88" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AN88" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO88" t="n">
         <v>0</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR88" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AS88" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AT88" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AU88" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AV88" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW88" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX88" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY88" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ88" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BA88" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BB88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC88" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD88" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE88" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF88" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>6.61</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20313,124 +20313,124 @@
         <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U101" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V101" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W101" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG101" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AH101" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI101" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AJ101" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK101" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL101" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM101" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AN101" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO101" t="n">
         <v>0</v>
       </c>
       <c r="AP101" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR101" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS101" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AU101" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AV101" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW101" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX101" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY101" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ101" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA101" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BB101" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC101" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD101" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE101" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF101" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R118" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25477,10 +25477,10 @@
         <v>0</v>
       </c>
       <c r="AG127" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH127" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q152" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -32667,22 +32667,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32711,7 +32711,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -32864,22 +32864,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32908,7 +32908,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,22 +34243,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q190" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q191" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R191" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40201,13 +40201,13 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q202" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R202" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S202" t="n">
         <v>0</v>
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q205" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R205" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,22 +43108,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,22 +44290,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,22 +45669,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,22 +46260,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,22 +47836,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,22 +48033,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49412,22 +49412,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G267" t="n">

--- a/jogos_2026-05-16.xlsx
+++ b/jogos_2026-05-16.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.67</v>
+        <v>4.08</v>
       </c>
       <c r="R53" t="n">
-        <v>3.47</v>
+        <v>4.75</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.62</v>
+        <v>2.23</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.93</v>
+        <v>2.78</v>
       </c>
       <c r="R64" t="n">
-        <v>2.58</v>
+        <v>3.43</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.37</v>
+        <v>2.62</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="R69" t="n">
-        <v>2.11</v>
+        <v>2.58</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.23</v>
+        <v>3.37</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="R70" t="n">
-        <v>3.43</v>
+        <v>2.11</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.31</v>
+        <v>3.49</v>
       </c>
       <c r="R79" t="n">
-        <v>2.09</v>
+        <v>2.72</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.48</v>
+        <v>1.28</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.19</v>
+        <v>7.13</v>
       </c>
       <c r="R80" t="n">
-        <v>2.05</v>
+        <v>11</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3.7</v>
+        <v>2.82</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.52</v>
+        <v>4.1</v>
       </c>
       <c r="R81" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.77</v>
+        <v>1.45</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.41</v>
+        <v>5.95</v>
       </c>
       <c r="R82" t="n">
-        <v>2.34</v>
+        <v>6.36</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.45</v>
+        <v>2.77</v>
       </c>
       <c r="Q83" t="n">
-        <v>5.95</v>
+        <v>4.41</v>
       </c>
       <c r="R83" t="n">
-        <v>6.36</v>
+        <v>2.34</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.82</v>
+        <v>3.28</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.1</v>
+        <v>4.31</v>
       </c>
       <c r="R84" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.28</v>
+        <v>3.7</v>
       </c>
       <c r="Q85" t="n">
-        <v>7.13</v>
+        <v>4.52</v>
       </c>
       <c r="R85" t="n">
-        <v>11</v>
+        <v>1.91</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.77</v>
+        <v>3.48</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.49</v>
+        <v>4.19</v>
       </c>
       <c r="R86" t="n">
-        <v>2.72</v>
+        <v>2.05</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>6.61</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.43</v>
+        <v>1.78</v>
       </c>
       <c r="Q92" t="n">
-        <v>5.06</v>
+        <v>4.13</v>
       </c>
       <c r="R92" t="n">
-        <v>6.61</v>
+        <v>4.13</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,133 +18728,133 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI93" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AJ93" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK93" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL93" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM93" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AN93" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO93" t="n">
         <v>0</v>
       </c>
       <c r="AP93" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR93" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS93" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AU93" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AV93" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW93" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX93" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY93" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ93" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA93" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BB93" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC93" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD93" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE93" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF93" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.13</v>
+        <v>3.87</v>
       </c>
       <c r="R95" t="n">
-        <v>4.13</v>
+        <v>3.92</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>5.73</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,133 +20304,133 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S101" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U101" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AH101" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI101" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AJ101" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK101" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL101" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM101" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AN101" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO101" t="n">
         <v>0</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR101" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AS101" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AT101" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AU101" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AV101" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW101" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX101" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY101" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ101" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BA101" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BB101" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC101" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD101" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE101" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF101" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.22</v>
+        <v>3.63</v>
       </c>
       <c r="R104" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.96</v>
+        <v>3.06</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.63</v>
+        <v>3.22</v>
       </c>
       <c r="R105" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="Q116" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R116" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>3.91</v>
+        <v>1.79</v>
       </c>
       <c r="Q127" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="R127" t="n">
-        <v>1.65</v>
+        <v>3.7</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25477,10 +25477,10 @@
         <v>0</v>
       </c>
       <c r="AG127" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH127" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>6.15</v>
+        <v>3.91</v>
       </c>
       <c r="Q128" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="R128" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25674,10 +25674,10 @@
         <v>0</v>
       </c>
       <c r="AG128" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH128" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI128" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1.79</v>
+        <v>6.15</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="R130" t="n">
-        <v>3.7</v>
+        <v>1.46</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28924,22 +28924,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R148" t="n">
         <v>2.07</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R148" t="n">
-        <v>3.64</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="R149" t="n">
-        <v>4.09</v>
+        <v>2.8</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,22 +29909,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>2.46</v>
+        <v>2.07</v>
       </c>
       <c r="Q152" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R152" t="n">
-        <v>3.11</v>
+        <v>3.64</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2.5</v>
+        <v>4.08</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="R153" t="n">
-        <v>2.8</v>
+        <v>1.69</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32667,22 +32667,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32711,7 +32711,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -32864,22 +32864,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32908,7 +32908,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P165" t="n">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q192" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40201,13 +40201,13 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q202" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R202" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S202" t="n">
         <v>0</v>
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q207" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R207" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,22 +42123,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF212" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,22 +43896,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,22 +45472,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,22 +45669,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,22 +46260,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,22 +46457,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,22 +46654,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,22 +47836,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,22 +48033,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,22 +50397,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50445,13 +50445,13 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q254" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R254" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="S254" t="n">
         <v>0</v>
@@ -50490,10 +50490,10 @@
         <v>0</v>
       </c>
       <c r="AE254" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF254" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG254" t="n">
         <v>0</v>
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G267" t="n">

--- a/jogos_2026-05-16.xlsx
+++ b/jogos_2026-05-16.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.67</v>
+        <v>3.36</v>
       </c>
       <c r="Q19" t="n">
         <v>3.46</v>
       </c>
       <c r="R19" t="n">
-        <v>1.84</v>
+        <v>2.18</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.23</v>
+        <v>1.72</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.78</v>
+        <v>3.74</v>
       </c>
       <c r="R64" t="n">
-        <v>3.43</v>
+        <v>4.6</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>3.37</v>
+        <v>1.5</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="R70" t="n">
-        <v>2.11</v>
+        <v>6.19</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.98</v>
+        <v>3.23</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R78" t="n">
-        <v>3.78</v>
+        <v>2.11</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.49</v>
+        <v>4.1</v>
       </c>
       <c r="R79" t="n">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.1</v>
+        <v>3.49</v>
       </c>
       <c r="R81" t="n">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.31</v>
+        <v>4.52</v>
       </c>
       <c r="R84" t="n">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.52</v>
+        <v>4.19</v>
       </c>
       <c r="R85" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>3.48</v>
+        <v>2.57</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
       <c r="R86" t="n">
-        <v>2.05</v>
+        <v>2.57</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.57</v>
+        <v>3.28</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.22</v>
+        <v>4.31</v>
       </c>
       <c r="R87" t="n">
-        <v>2.57</v>
+        <v>2.09</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.76</v>
+        <v>3.87</v>
       </c>
       <c r="R89" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>6.61</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,133 +18334,133 @@
         </is>
       </c>
       <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T91" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U91" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V91" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W91" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X91" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP91" t="n">
         <v>1.32</v>
       </c>
-      <c r="Q91" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="R91" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" t="n">
-        <v>0</v>
-      </c>
-      <c r="W91" t="n">
-        <v>0</v>
-      </c>
-      <c r="X91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP91" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ91" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR91" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS91" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AU91" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AV91" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW91" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX91" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY91" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ91" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA91" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BB91" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC91" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD91" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE91" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF91" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,133 +18728,133 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="S93" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AJ93" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK93" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL93" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM93" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AN93" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO93" t="n">
         <v>0</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR93" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AS93" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AT93" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AU93" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AV93" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW93" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX93" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY93" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ93" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BA93" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BB93" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC93" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD93" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE93" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF93" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>6.61</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q121" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R121" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="R127" t="n">
-        <v>3.7</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>3.91</v>
+        <v>6.15</v>
       </c>
       <c r="Q128" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="R128" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25674,10 +25674,10 @@
         <v>0</v>
       </c>
       <c r="AG128" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH128" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI128" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1.25</v>
+        <v>3.91</v>
       </c>
       <c r="Q129" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="R129" t="n">
-        <v>9.050000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25871,10 +25871,10 @@
         <v>0</v>
       </c>
       <c r="AG129" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH129" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>6.15</v>
+        <v>1.79</v>
       </c>
       <c r="Q130" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="R130" t="n">
-        <v>1.46</v>
+        <v>3.7</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,22 +27939,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R149" t="n">
-        <v>2.8</v>
+        <v>3.11</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="Q150" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R150" t="n">
-        <v>3.11</v>
+        <v>2.65</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="R152" t="n">
-        <v>3.64</v>
+        <v>4.09</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="R154" t="n">
-        <v>2.65</v>
+        <v>2.07</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,22 +33849,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,22 +34243,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q175" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q190" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R190" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q191" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q200" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R200" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R207" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,22 +45078,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45126,13 +45126,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q227" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R227" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
@@ -45171,10 +45171,10 @@
         <v>0</v>
       </c>
       <c r="AE227" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF227" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG227" t="n">
         <v>0</v>
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,22 +45472,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,22 +46457,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,22 +46654,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,22 +47442,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,22 +48427,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,22 +50397,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50445,13 +50445,13 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q254" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R254" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="S254" t="n">
         <v>0</v>
@@ -50490,10 +50490,10 @@
         <v>0</v>
       </c>
       <c r="AE254" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF254" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG254" t="n">
         <v>0</v>
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,22 +50988,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G267" t="n">

--- a/jogos_2026-05-16.xlsx
+++ b/jogos_2026-05-16.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.36</v>
+        <v>4.67</v>
       </c>
       <c r="Q19" t="n">
         <v>3.46</v>
       </c>
       <c r="R19" t="n">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.72</v>
+        <v>2.62</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.74</v>
+        <v>2.93</v>
       </c>
       <c r="R64" t="n">
-        <v>4.6</v>
+        <v>2.58</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.62</v>
+        <v>2.23</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.93</v>
+        <v>2.78</v>
       </c>
       <c r="R69" t="n">
-        <v>2.58</v>
+        <v>3.43</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.82</v>
+        <v>2.57</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.1</v>
+        <v>4.22</v>
       </c>
       <c r="R79" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.28</v>
+        <v>3.48</v>
       </c>
       <c r="Q80" t="n">
-        <v>7.13</v>
+        <v>4.19</v>
       </c>
       <c r="R80" t="n">
-        <v>11</v>
+        <v>2.05</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.49</v>
+        <v>4.31</v>
       </c>
       <c r="R81" t="n">
-        <v>2.72</v>
+        <v>2.09</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.45</v>
+        <v>2.77</v>
       </c>
       <c r="Q82" t="n">
-        <v>5.95</v>
+        <v>4.41</v>
       </c>
       <c r="R82" t="n">
-        <v>6.36</v>
+        <v>2.34</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.77</v>
+        <v>1.45</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.41</v>
+        <v>5.95</v>
       </c>
       <c r="R83" t="n">
-        <v>2.34</v>
+        <v>6.36</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>3.7</v>
+        <v>2.82</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.52</v>
+        <v>4.1</v>
       </c>
       <c r="R84" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>3.48</v>
+        <v>1.28</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.19</v>
+        <v>7.13</v>
       </c>
       <c r="R85" t="n">
-        <v>2.05</v>
+        <v>11</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.57</v>
+        <v>3.7</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.22</v>
+        <v>4.52</v>
       </c>
       <c r="R86" t="n">
-        <v>2.57</v>
+        <v>1.91</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.31</v>
+        <v>3.49</v>
       </c>
       <c r="R87" t="n">
-        <v>2.09</v>
+        <v>2.72</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.76</v>
+        <v>3.87</v>
       </c>
       <c r="R88" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,133 +18334,133 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S91" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI91" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AJ91" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK91" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL91" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM91" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AN91" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO91" t="n">
         <v>0</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR91" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AS91" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AT91" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AU91" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AV91" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW91" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX91" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY91" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ91" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BA91" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BB91" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC91" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD91" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE91" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF91" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18540,124 +18540,124 @@
         <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U92" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V92" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD92" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG92" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AH92" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI92" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AJ92" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK92" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL92" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM92" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AN92" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO92" t="n">
         <v>0</v>
       </c>
       <c r="AP92" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR92" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS92" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AU92" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AV92" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW92" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX92" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY92" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ92" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA92" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BB92" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC92" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD92" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE92" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF92" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>6.61</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>6.61</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.87</v>
+        <v>3.76</v>
       </c>
       <c r="R102" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>5.73</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.96</v>
+        <v>3.06</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.63</v>
+        <v>3.22</v>
       </c>
       <c r="R104" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.22</v>
+        <v>3.63</v>
       </c>
       <c r="R105" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>6.15</v>
+        <v>1.79</v>
       </c>
       <c r="Q128" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="R128" t="n">
-        <v>1.46</v>
+        <v>3.7</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>3.91</v>
+        <v>6.15</v>
       </c>
       <c r="Q129" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="R129" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25871,10 +25871,10 @@
         <v>0</v>
       </c>
       <c r="AG129" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH129" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1.79</v>
+        <v>3.91</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="R130" t="n">
-        <v>3.7</v>
+        <v>1.65</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26068,10 +26068,10 @@
         <v>0</v>
       </c>
       <c r="AG130" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH130" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,22 +27545,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>2.14</v>
+        <v>2.75</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R141" t="n">
-        <v>3.38</v>
+        <v>2.65</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.5</v>
+        <v>4.08</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="R147" t="n">
-        <v>2.8</v>
+        <v>1.69</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,22 +29515,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,22 +33849,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,22 +34243,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q176" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q179" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37837,13 +37837,13 @@
         </is>
       </c>
       <c r="P190" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q190" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q192" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q193" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R193" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -39759,7 +39759,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39807,13 +39807,13 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q200" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R200" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40201,13 +40201,13 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q202" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R202" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S202" t="n">
         <v>0</v>
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,22 +43896,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,22 +45078,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45126,13 +45126,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q227" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
@@ -45171,10 +45171,10 @@
         <v>0</v>
       </c>
       <c r="AE227" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF227" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG227" t="n">
         <v>0</v>
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,22 +46260,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,22 +46457,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q234" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R234" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46550,10 +46550,10 @@
         <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF234" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG234" t="n">
         <v>0</v>
@@ -46654,22 +46654,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,22 +47442,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,22 +48427,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,22 +50791,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,22 +50988,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,22 +51185,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G262" t="n">

--- a/jogos_2026-05-16.xlsx
+++ b/jogos_2026-05-16.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3216,10 +3216,10 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="R69" t="n">
-        <v>3.43</v>
+        <v>3.78</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.37</v>
+        <v>1.89</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="R73" t="n">
-        <v>2.11</v>
+        <v>4.29</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.72</v>
+        <v>2.23</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.74</v>
+        <v>2.78</v>
       </c>
       <c r="R74" t="n">
-        <v>4.6</v>
+        <v>3.43</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.57</v>
+        <v>3.7</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.22</v>
+        <v>4.52</v>
       </c>
       <c r="R79" t="n">
-        <v>2.57</v>
+        <v>1.91</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.19</v>
+        <v>4.31</v>
       </c>
       <c r="R80" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.31</v>
+        <v>3.49</v>
       </c>
       <c r="R81" t="n">
-        <v>2.09</v>
+        <v>2.72</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>3.7</v>
+        <v>2.57</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.52</v>
+        <v>4.22</v>
       </c>
       <c r="R86" t="n">
-        <v>1.91</v>
+        <v>2.57</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.77</v>
+        <v>3.48</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.49</v>
+        <v>4.19</v>
       </c>
       <c r="R87" t="n">
-        <v>2.72</v>
+        <v>2.05</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.87</v>
+        <v>5.06</v>
       </c>
       <c r="R91" t="n">
-        <v>3.46</v>
+        <v>6.61</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,133 +18531,133 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S92" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI92" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AJ92" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK92" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL92" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM92" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AN92" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO92" t="n">
         <v>0</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR92" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AS92" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AT92" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AU92" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AV92" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW92" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX92" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY92" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ92" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BA92" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BB92" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC92" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD92" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE92" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF92" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18737,124 +18737,124 @@
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI93" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AJ93" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK93" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL93" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM93" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AN93" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO93" t="n">
         <v>0</v>
       </c>
       <c r="AP93" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR93" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS93" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AU93" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AV93" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW93" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX93" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY93" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ93" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA93" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BB93" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC93" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD93" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE93" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF93" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG93" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="Q99" t="n">
-        <v>4.13</v>
+        <v>3.87</v>
       </c>
       <c r="R99" t="n">
-        <v>4.13</v>
+        <v>3.92</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>6.61</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.22</v>
+        <v>3.63</v>
       </c>
       <c r="R104" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.96</v>
+        <v>3.06</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.63</v>
+        <v>3.22</v>
       </c>
       <c r="R105" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.25</v>
+        <v>6.15</v>
       </c>
       <c r="Q127" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="R127" t="n">
-        <v>9.050000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="R128" t="n">
-        <v>3.7</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>6.15</v>
+        <v>1.79</v>
       </c>
       <c r="Q129" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="R129" t="n">
-        <v>1.46</v>
+        <v>3.7</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.14</v>
+        <v>2.75</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R140" t="n">
-        <v>3.38</v>
+        <v>2.65</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R141" t="n">
-        <v>2.65</v>
+        <v>3.11</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>3.16</v>
+        <v>2.07</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="R142" t="n">
-        <v>2.07</v>
+        <v>3.64</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R143" t="n">
-        <v>2.8</v>
+        <v>3.38</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q144" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R144" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="R145" t="n">
-        <v>3.64</v>
+        <v>4.09</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,22 +33849,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,22 +34243,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q172" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R172" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35425,22 +35425,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q178" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35622,22 +35622,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q179" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q191" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R191" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38079,10 +38079,10 @@
         <v>0</v>
       </c>
       <c r="AE191" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF191" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG191" t="n">
         <v>0</v>
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q193" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,22 +41729,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q210" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R210" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41822,10 +41822,10 @@
         <v>0</v>
       </c>
       <c r="AE210" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF210" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG210" t="n">
         <v>0</v>
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q216" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,22 +46260,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,22 +46457,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46505,13 +46505,13 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q234" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -46550,10 +46550,10 @@
         <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF234" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG234" t="n">
         <v>0</v>
@@ -46654,22 +46654,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49806,22 +49806,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,22 +50200,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,22 +50791,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,22 +51185,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51579,22 +51579,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G263" t="n">

--- a/jogos_2026-05-16.xlsx
+++ b/jogos_2026-05-16.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.67</v>
+        <v>3.36</v>
       </c>
       <c r="Q16" t="n">
         <v>3.46</v>
       </c>
       <c r="R16" t="n">
-        <v>1.84</v>
+        <v>2.18</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.69</v>
+        <v>2.08</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.08</v>
+        <v>3.67</v>
       </c>
       <c r="R49" t="n">
-        <v>4.75</v>
+        <v>3.47</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.37</v>
+        <v>1.89</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="R65" t="n">
-        <v>2.11</v>
+        <v>4.29</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.72</v>
+        <v>2.23</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.74</v>
+        <v>2.78</v>
       </c>
       <c r="R67" t="n">
-        <v>4.6</v>
+        <v>3.43</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.15</v>
+        <v>1.72</v>
       </c>
       <c r="Q71" t="n">
-        <v>5.5</v>
+        <v>3.74</v>
       </c>
       <c r="R71" t="n">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.7</v>
+        <v>1.28</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.52</v>
+        <v>7.13</v>
       </c>
       <c r="R79" t="n">
-        <v>1.91</v>
+        <v>11</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.28</v>
+        <v>2.57</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.31</v>
+        <v>4.22</v>
       </c>
       <c r="R80" t="n">
-        <v>2.09</v>
+        <v>2.57</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16367,10 +16367,10 @@
         <v>2.77</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.49</v>
+        <v>4.41</v>
       </c>
       <c r="R81" t="n">
-        <v>2.72</v>
+        <v>2.34</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.41</v>
+        <v>4.31</v>
       </c>
       <c r="R82" t="n">
-        <v>2.34</v>
+        <v>2.09</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.45</v>
+        <v>2.82</v>
       </c>
       <c r="Q83" t="n">
-        <v>5.95</v>
+        <v>4.1</v>
       </c>
       <c r="R83" t="n">
-        <v>6.36</v>
+        <v>2.4</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.82</v>
+        <v>3.48</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.1</v>
+        <v>4.19</v>
       </c>
       <c r="R84" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.28</v>
+        <v>2.77</v>
       </c>
       <c r="Q85" t="n">
-        <v>7.13</v>
+        <v>3.49</v>
       </c>
       <c r="R85" t="n">
-        <v>11</v>
+        <v>2.72</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.57</v>
+        <v>1.45</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.22</v>
+        <v>5.95</v>
       </c>
       <c r="R86" t="n">
-        <v>2.57</v>
+        <v>6.36</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.19</v>
+        <v>4.52</v>
       </c>
       <c r="R87" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>6.61</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.76</v>
+        <v>4.13</v>
       </c>
       <c r="R92" t="n">
-        <v>3.5</v>
+        <v>4.13</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18737,124 +18737,124 @@
         <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AJ93" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK93" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL93" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM93" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AN93" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO93" t="n">
         <v>0</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR93" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AS93" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AT93" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AU93" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AV93" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW93" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX93" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY93" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ93" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BA93" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BB93" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC93" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD93" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE93" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF93" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>6.61</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19722,124 +19722,124 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V98" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG98" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AH98" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI98" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK98" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL98" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM98" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AN98" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO98" t="n">
         <v>0</v>
       </c>
       <c r="AP98" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR98" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS98" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AU98" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AV98" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW98" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX98" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY98" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ98" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA98" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BB98" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD98" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE98" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF98" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="Q103" t="n">
-        <v>4.13</v>
+        <v>3.87</v>
       </c>
       <c r="R103" t="n">
-        <v>4.13</v>
+        <v>3.46</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.96</v>
+        <v>3.06</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.63</v>
+        <v>3.22</v>
       </c>
       <c r="R104" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.22</v>
+        <v>3.63</v>
       </c>
       <c r="R105" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>6.15</v>
+        <v>1.25</v>
       </c>
       <c r="Q127" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="R127" t="n">
-        <v>1.46</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="Q128" t="n">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="R128" t="n">
-        <v>9.050000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1.79</v>
+        <v>6.15</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="R129" t="n">
-        <v>3.7</v>
+        <v>1.46</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="Q141" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R141" t="n">
-        <v>3.11</v>
+        <v>2.65</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>2.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="R142" t="n">
-        <v>3.64</v>
+        <v>1.69</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R144" t="n">
-        <v>2.8</v>
+        <v>3.11</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,22 +29121,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>3.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="R149" t="n">
-        <v>2.07</v>
+        <v>3.38</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -31879,22 +31879,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>2.12</v>
+        <v>2.54</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.62</v>
+        <v>3.01</v>
       </c>
       <c r="R161" t="n">
-        <v>3.41</v>
+        <v>3.17</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q163" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32667,22 +32667,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32711,7 +32711,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -32864,22 +32864,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32908,7 +32908,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P165" t="n">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q168" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33548,10 +33548,10 @@
         <v>0</v>
       </c>
       <c r="AE168" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF168" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG168" t="n">
         <v>0</v>
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q175" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q179" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35721,10 +35721,10 @@
         <v>0</v>
       </c>
       <c r="AG179" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH179" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI179" t="n">
         <v>0</v>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38034,13 +38034,13 @@
         </is>
       </c>
       <c r="P191" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q191" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R191" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -38079,10 +38079,10 @@
         <v>0</v>
       </c>
       <c r="AE191" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF191" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG191" t="n">
         <v>0</v>
@@ -38183,7 +38183,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q192" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38276,10 +38276,10 @@
         <v>0</v>
       </c>
       <c r="AE192" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF192" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="R194" t="n">
-        <v>4.32</v>
+        <v>3.83</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="R195" t="n">
-        <v>3.83</v>
+        <v>4.32</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39956,7 +39956,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40153,7 +40153,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40201,13 +40201,13 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q202" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R202" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S202" t="n">
         <v>0</v>
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q207" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R207" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,22 +41532,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,22 +41729,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q210" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41822,10 +41822,10 @@
         <v>0</v>
       </c>
       <c r="AE210" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF210" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG210" t="n">
         <v>0</v>
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -42959,13 +42959,13 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q216" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,22 +45866,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,22 +46260,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,22 +47048,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,13 +47096,13 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q237" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R237" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="S237" t="n">
         <v>0</v>
@@ -47141,10 +47141,10 @@
         <v>0</v>
       </c>
       <c r="AE237" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF237" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG237" t="n">
         <v>0</v>
@@ -47245,7 +47245,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,22 +49806,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,22 +50200,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,22 +50988,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51036,13 +51036,13 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q257" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="R257" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S257" t="n">
         <v>0</v>
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51579,22 +51579,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51973,7 +51973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52170,7 +52170,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G267" t="n">

--- a/jogos_2026-05-16.xlsx
+++ b/jogos_2026-05-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI269"/>
+  <dimension ref="A1:BI273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.68</v>
+        <v>2.93</v>
       </c>
       <c r="R66" t="n">
-        <v>6.19</v>
+        <v>2.58</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,10 +13803,10 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.23</v>
+        <v>3.37</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R68" t="n">
         <v>2.11</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.98</v>
+        <v>2.23</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="R69" t="n">
-        <v>3.78</v>
+        <v>3.43</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.72</v>
+        <v>3.23</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.74</v>
+        <v>3.35</v>
       </c>
       <c r="R71" t="n">
-        <v>4.6</v>
+        <v>2.11</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.62</v>
+        <v>1.72</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.93</v>
+        <v>3.74</v>
       </c>
       <c r="R75" t="n">
-        <v>2.58</v>
+        <v>4.6</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.28</v>
+        <v>2.82</v>
       </c>
       <c r="Q79" t="n">
-        <v>7.13</v>
+        <v>4.1</v>
       </c>
       <c r="R79" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.57</v>
+        <v>1.28</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.22</v>
+        <v>7.13</v>
       </c>
       <c r="R80" t="n">
-        <v>2.57</v>
+        <v>11</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16367,10 +16367,10 @@
         <v>2.77</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.41</v>
+        <v>3.49</v>
       </c>
       <c r="R81" t="n">
-        <v>2.34</v>
+        <v>2.72</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>3.28</v>
+        <v>1.45</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.31</v>
+        <v>5.95</v>
       </c>
       <c r="R82" t="n">
-        <v>2.09</v>
+        <v>6.36</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.1</v>
+        <v>4.41</v>
       </c>
       <c r="R83" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>3.48</v>
+        <v>2.57</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
       <c r="R84" t="n">
-        <v>2.05</v>
+        <v>2.57</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.77</v>
+        <v>3.7</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.49</v>
+        <v>4.52</v>
       </c>
       <c r="R85" t="n">
-        <v>2.72</v>
+        <v>1.91</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.45</v>
+        <v>3.48</v>
       </c>
       <c r="Q86" t="n">
-        <v>5.95</v>
+        <v>4.19</v>
       </c>
       <c r="R86" t="n">
-        <v>6.36</v>
+        <v>2.05</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.52</v>
+        <v>4.31</v>
       </c>
       <c r="R87" t="n">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.78</v>
+        <v>1.43</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.13</v>
+        <v>5.06</v>
       </c>
       <c r="R92" t="n">
-        <v>4.13</v>
+        <v>6.61</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="Q95" t="n">
-        <v>5.06</v>
+        <v>5.73</v>
       </c>
       <c r="R95" t="n">
-        <v>6.61</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19328,124 +19328,124 @@
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V96" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W96" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG96" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AH96" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI96" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AJ96" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK96" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL96" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM96" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AN96" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO96" t="n">
         <v>0</v>
       </c>
       <c r="AP96" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR96" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS96" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AT96" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AU96" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AV96" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW96" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX96" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY96" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ96" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA96" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BB96" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC96" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD96" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE96" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF96" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>5.73</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,133 +19713,133 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="S98" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U98" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V98" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AH98" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI98" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AJ98" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK98" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL98" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM98" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AN98" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO98" t="n">
         <v>0</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR98" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AS98" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AT98" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AU98" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AV98" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW98" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX98" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY98" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ98" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BA98" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BB98" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC98" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD98" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE98" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF98" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.76</v>
+        <v>3.87</v>
       </c>
       <c r="R101" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.22</v>
+        <v>3.63</v>
       </c>
       <c r="R104" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.96</v>
+        <v>3.06</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.63</v>
+        <v>3.22</v>
       </c>
       <c r="R105" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.98</v>
+        <v>2</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R113" t="n">
-        <v>2.21</v>
+        <v>3.3</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="Q127" t="n">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="R127" t="n">
-        <v>9.050000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.79</v>
+        <v>3.91</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="R128" t="n">
-        <v>3.7</v>
+        <v>1.65</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25674,10 +25674,10 @@
         <v>0</v>
       </c>
       <c r="AG128" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH128" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI128" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>6.15</v>
+        <v>1.25</v>
       </c>
       <c r="Q129" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="R129" t="n">
-        <v>1.46</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>3.91</v>
+        <v>6.15</v>
       </c>
       <c r="Q130" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="R130" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26068,10 +26068,10 @@
         <v>0</v>
       </c>
       <c r="AG130" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH130" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI130" t="n">
         <v>0</v>
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,22 +28530,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="R146" t="n">
-        <v>4.09</v>
+        <v>3.64</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,22 +29318,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>3.16</v>
+        <v>4.08</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="R148" t="n">
-        <v>2.07</v>
+        <v>1.69</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R149" t="n">
-        <v>3.38</v>
+        <v>2.8</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q150" t="n">
         <v>3.1</v>
       </c>
       <c r="R150" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>2.07</v>
+        <v>2.46</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R154" t="n">
-        <v>3.64</v>
+        <v>3.11</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="Q159" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="R159" t="n">
-        <v>4.26</v>
+        <v>3.41</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>2.54</v>
+        <v>1.8</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.01</v>
+        <v>4</v>
       </c>
       <c r="R161" t="n">
-        <v>3.17</v>
+        <v>4.26</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32273,22 +32273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -32667,22 +32667,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -32711,7 +32711,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -32864,22 +32864,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32908,7 +32908,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33351,10 +33351,10 @@
         <v>0</v>
       </c>
       <c r="AE167" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF167" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG167" t="n">
         <v>0</v>
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33548,10 +33548,10 @@
         <v>0</v>
       </c>
       <c r="AE168" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF168" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,22 +33849,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34243,22 +34243,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q172" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34632,12 +34632,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34820,7 +34820,7 @@
         <v>0</v>
       </c>
       <c r="BI174" s="3" t="n">
-        <v>46158.63541666666</v>
+        <v>46158.625</v>
       </c>
     </row>
     <row r="175">
@@ -34829,12 +34829,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35017,7 +35017,7 @@
         <v>0</v>
       </c>
       <c r="BI175" s="3" t="n">
-        <v>46158.63541666666</v>
+        <v>46158.625</v>
       </c>
     </row>
     <row r="176">
@@ -35026,12 +35026,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>4.83</v>
+        <v>1.97</v>
       </c>
       <c r="Q176" t="n">
-        <v>3.5</v>
+        <v>4.02</v>
       </c>
       <c r="R176" t="n">
-        <v>1.65</v>
+        <v>3.45</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35214,7 +35214,7 @@
         <v>0</v>
       </c>
       <c r="BI176" s="3" t="n">
-        <v>46158.64583333334</v>
+        <v>46158.625</v>
       </c>
     </row>
     <row r="177">
@@ -35223,27 +35223,27 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35411,7 +35411,7 @@
         <v>0</v>
       </c>
       <c r="BI177" s="3" t="n">
-        <v>46158.64583333334</v>
+        <v>46158.625</v>
       </c>
     </row>
     <row r="178">
@@ -35420,27 +35420,27 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="Q178" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="R178" t="n">
-        <v>2.65</v>
+        <v>2.01</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35608,7 +35608,7 @@
         <v>0</v>
       </c>
       <c r="BI178" s="3" t="n">
-        <v>46158.65625</v>
+        <v>46158.63541666666</v>
       </c>
     </row>
     <row r="179">
@@ -35617,12 +35617,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q179" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35721,10 +35721,10 @@
         <v>0</v>
       </c>
       <c r="AG179" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH179" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI179" t="n">
         <v>0</v>
@@ -35805,7 +35805,7 @@
         <v>0</v>
       </c>
       <c r="BI179" s="3" t="n">
-        <v>46158.65625</v>
+        <v>46158.63541666666</v>
       </c>
     </row>
     <row r="180">
@@ -35814,12 +35814,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q180" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36002,7 +36002,7 @@
         <v>0</v>
       </c>
       <c r="BI180" s="3" t="n">
-        <v>46158.66666666666</v>
+        <v>46158.64583333334</v>
       </c>
     </row>
     <row r="181">
@@ -36011,12 +36011,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36199,7 +36199,7 @@
         <v>0</v>
       </c>
       <c r="BI181" s="3" t="n">
-        <v>46158.66666666666</v>
+        <v>46158.64583333334</v>
       </c>
     </row>
     <row r="182">
@@ -36208,27 +36208,27 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q182" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36312,10 +36312,10 @@
         <v>0</v>
       </c>
       <c r="AG182" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH182" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI182" t="n">
         <v>0</v>
@@ -36396,7 +36396,7 @@
         <v>0</v>
       </c>
       <c r="BI182" s="3" t="n">
-        <v>46158.66666666666</v>
+        <v>46158.65625</v>
       </c>
     </row>
     <row r="183">
@@ -36405,12 +36405,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36593,7 +36593,7 @@
         <v>0</v>
       </c>
       <c r="BI183" s="3" t="n">
-        <v>46158.66666666666</v>
+        <v>46158.65625</v>
       </c>
     </row>
     <row r="184">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37390,12 +37390,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37578,7 +37578,7 @@
         <v>0</v>
       </c>
       <c r="BI188" s="3" t="n">
-        <v>46158.72916666666</v>
+        <v>46158.66666666666</v>
       </c>
     </row>
     <row r="189">
@@ -37587,7 +37587,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="BI189" s="3" t="n">
-        <v>46158.76041666666</v>
+        <v>46158.66666666666</v>
       </c>
     </row>
     <row r="190">
@@ -37784,12 +37784,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37972,7 +37972,7 @@
         <v>0</v>
       </c>
       <c r="BI190" s="3" t="n">
-        <v>46158.77083333334</v>
+        <v>46158.66666666666</v>
       </c>
     </row>
     <row r="191">
@@ -37981,12 +37981,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38169,7 +38169,7 @@
         <v>0</v>
       </c>
       <c r="BI191" s="3" t="n">
-        <v>46158.77083333334</v>
+        <v>46158.66666666666</v>
       </c>
     </row>
     <row r="192">
@@ -38178,12 +38178,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38231,13 +38231,13 @@
         </is>
       </c>
       <c r="P192" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -38276,10 +38276,10 @@
         <v>0</v>
       </c>
       <c r="AE192" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF192" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -38366,7 +38366,7 @@
         <v>0</v>
       </c>
       <c r="BI192" s="3" t="n">
-        <v>46158.77083333334</v>
+        <v>46158.72916666666</v>
       </c>
     </row>
     <row r="193">
@@ -38375,12 +38375,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38563,7 +38563,7 @@
         <v>0</v>
       </c>
       <c r="BI193" s="3" t="n">
-        <v>46158.77083333334</v>
+        <v>46158.76041666666</v>
       </c>
     </row>
     <row r="194">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="R195" t="n">
-        <v>4.32</v>
+        <v>3.83</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38966,12 +38966,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q196" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF196" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39154,7 +39154,7 @@
         <v>0</v>
       </c>
       <c r="BI196" s="3" t="n">
-        <v>46158.79166666666</v>
+        <v>46158.77083333334</v>
       </c>
     </row>
     <row r="197">
@@ -39163,12 +39163,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q197" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39351,7 +39351,7 @@
         <v>0</v>
       </c>
       <c r="BI197" s="3" t="n">
-        <v>46158.79166666666</v>
+        <v>46158.77083333334</v>
       </c>
     </row>
     <row r="198">
@@ -39360,12 +39360,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39548,7 +39548,7 @@
         <v>0</v>
       </c>
       <c r="BI198" s="3" t="n">
-        <v>46158.8125</v>
+        <v>46158.77083333334</v>
       </c>
     </row>
     <row r="199">
@@ -39557,12 +39557,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39745,7 +39745,7 @@
         <v>0</v>
       </c>
       <c r="BI199" s="3" t="n">
-        <v>46158.85416666666</v>
+        <v>46158.77083333334</v>
       </c>
     </row>
     <row r="200">
@@ -39754,12 +39754,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39942,7 +39942,7 @@
         <v>0</v>
       </c>
       <c r="BI200" s="3" t="n">
-        <v>46158.85416666666</v>
+        <v>46158.79166666666</v>
       </c>
     </row>
     <row r="201">
@@ -39951,12 +39951,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40139,7 +40139,7 @@
         <v>0</v>
       </c>
       <c r="BI201" s="3" t="n">
-        <v>46158.85416666666</v>
+        <v>46158.79166666666</v>
       </c>
     </row>
     <row r="202">
@@ -40148,12 +40148,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40336,7 +40336,7 @@
         <v>0</v>
       </c>
       <c r="BI202" s="3" t="n">
-        <v>46158.85416666666</v>
+        <v>46158.8125</v>
       </c>
     </row>
     <row r="203">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q203" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R203" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R207" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41330,27 +41330,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41518,7 +41518,7 @@
         <v>0</v>
       </c>
       <c r="BI208" s="3" t="n">
-        <v>46158.875</v>
+        <v>46158.85416666666</v>
       </c>
     </row>
     <row r="209">
@@ -41527,12 +41527,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41715,7 +41715,7 @@
         <v>0</v>
       </c>
       <c r="BI209" s="3" t="n">
-        <v>46158.875</v>
+        <v>46158.85416666666</v>
       </c>
     </row>
     <row r="210">
@@ -41724,27 +41724,27 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41912,7 +41912,7 @@
         <v>0</v>
       </c>
       <c r="BI210" s="3" t="n">
-        <v>46158.875</v>
+        <v>46158.85416666666</v>
       </c>
     </row>
     <row r="211">
@@ -41921,27 +41921,27 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42109,7 +42109,7 @@
         <v>0</v>
       </c>
       <c r="BI211" s="3" t="n">
-        <v>46158.875</v>
+        <v>46158.85416666666</v>
       </c>
     </row>
     <row r="212">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,7 +43502,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -43512,12 +43512,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,22 +44290,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44881,22 +44881,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,22 +45472,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45520,13 +45520,13 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q229" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R229" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -45565,10 +45565,10 @@
         <v>0</v>
       </c>
       <c r="AE229" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF229" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG229" t="n">
         <v>0</v>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,22 +45866,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,22 +46260,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,22 +47048,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,13 +47096,13 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q237" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="S237" t="n">
         <v>0</v>
@@ -47141,10 +47141,10 @@
         <v>0</v>
       </c>
       <c r="AE237" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF237" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG237" t="n">
         <v>0</v>
@@ -47255,12 +47255,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,22 +48033,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,22 +50988,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51036,13 +51036,13 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q257" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S257" t="n">
         <v>0</v>
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51771,27 +51771,27 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51959,7 +51959,7 @@
         <v>0</v>
       </c>
       <c r="BI261" s="3" t="n">
-        <v>46158.89583333334</v>
+        <v>46158.875</v>
       </c>
     </row>
     <row r="262">
@@ -51968,27 +51968,27 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52156,7 +52156,7 @@
         <v>0</v>
       </c>
       <c r="BI262" s="3" t="n">
-        <v>46158.89583333334</v>
+        <v>46158.875</v>
       </c>
     </row>
     <row r="263">
@@ -52165,27 +52165,27 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52353,7 +52353,7 @@
         <v>0</v>
       </c>
       <c r="BI263" s="3" t="n">
-        <v>46158.89583333334</v>
+        <v>46158.875</v>
       </c>
     </row>
     <row r="264">
@@ -52362,12 +52362,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52415,13 +52415,13 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q264" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="R264" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S264" t="n">
         <v>0</v>
@@ -52550,7 +52550,7 @@
         <v>0</v>
       </c>
       <c r="BI264" s="3" t="n">
-        <v>46158.90625</v>
+        <v>46158.875</v>
       </c>
     </row>
     <row r="265">
@@ -52559,12 +52559,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -52574,12 +52574,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52747,7 +52747,7 @@
         <v>0</v>
       </c>
       <c r="BI265" s="3" t="n">
-        <v>46158.92708333334</v>
+        <v>46158.89583333334</v>
       </c>
     </row>
     <row r="266">
@@ -52756,7 +52756,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52944,7 +52944,7 @@
         <v>0</v>
       </c>
       <c r="BI266" s="3" t="n">
-        <v>46158.9375</v>
+        <v>46158.89583333334</v>
       </c>
     </row>
     <row r="267">
@@ -52953,7 +52953,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53141,7 +53141,7 @@
         <v>0</v>
       </c>
       <c r="BI267" s="3" t="n">
-        <v>46158.9375</v>
+        <v>46158.89583333334</v>
       </c>
     </row>
     <row r="268">
@@ -53150,12 +53150,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -53165,12 +53165,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -53338,7 +53338,7 @@
         <v>0</v>
       </c>
       <c r="BI268" s="3" t="n">
-        <v>46158.95833333334</v>
+        <v>46158.90625</v>
       </c>
     </row>
     <row r="269">
@@ -53347,7 +53347,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -53362,12 +53362,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -53535,6 +53535,794 @@
         <v>0</v>
       </c>
       <c r="BI269" s="3" t="n">
+        <v>46158.92708333334</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>0</v>
+      </c>
+      <c r="H270" t="n">
+        <v>0</v>
+      </c>
+      <c r="I270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="n">
+        <v>0</v>
+      </c>
+      <c r="L270" t="n">
+        <v>0</v>
+      </c>
+      <c r="M270" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N270" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P270" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>0</v>
+      </c>
+      <c r="R270" t="n">
+        <v>0</v>
+      </c>
+      <c r="S270" t="n">
+        <v>0</v>
+      </c>
+      <c r="T270" t="n">
+        <v>0</v>
+      </c>
+      <c r="U270" t="n">
+        <v>0</v>
+      </c>
+      <c r="V270" t="n">
+        <v>0</v>
+      </c>
+      <c r="W270" t="n">
+        <v>0</v>
+      </c>
+      <c r="X270" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ270" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA270" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB270" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC270" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD270" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE270" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF270" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG270" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH270" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI270" s="3" t="n">
+        <v>46158.9375</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0</v>
+      </c>
+      <c r="I271" t="n">
+        <v>0</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="n">
+        <v>0</v>
+      </c>
+      <c r="L271" t="n">
+        <v>0</v>
+      </c>
+      <c r="M271" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N271" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P271" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>0</v>
+      </c>
+      <c r="R271" t="n">
+        <v>0</v>
+      </c>
+      <c r="S271" t="n">
+        <v>0</v>
+      </c>
+      <c r="T271" t="n">
+        <v>0</v>
+      </c>
+      <c r="U271" t="n">
+        <v>0</v>
+      </c>
+      <c r="V271" t="n">
+        <v>0</v>
+      </c>
+      <c r="W271" t="n">
+        <v>0</v>
+      </c>
+      <c r="X271" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ271" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA271" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB271" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC271" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD271" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE271" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF271" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG271" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH271" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI271" s="3" t="n">
+        <v>46158.9375</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Los Angeles II</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>LA Galaxy II</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H272" t="n">
+        <v>0</v>
+      </c>
+      <c r="I272" t="n">
+        <v>0</v>
+      </c>
+      <c r="J272" t="n">
+        <v>0</v>
+      </c>
+      <c r="K272" t="n">
+        <v>0</v>
+      </c>
+      <c r="L272" t="n">
+        <v>0</v>
+      </c>
+      <c r="M272" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N272" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P272" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>0</v>
+      </c>
+      <c r="R272" t="n">
+        <v>0</v>
+      </c>
+      <c r="S272" t="n">
+        <v>0</v>
+      </c>
+      <c r="T272" t="n">
+        <v>0</v>
+      </c>
+      <c r="U272" t="n">
+        <v>0</v>
+      </c>
+      <c r="V272" t="n">
+        <v>0</v>
+      </c>
+      <c r="W272" t="n">
+        <v>0</v>
+      </c>
+      <c r="X272" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ272" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA272" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB272" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC272" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD272" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE272" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF272" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG272" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH272" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI272" s="3" t="n">
+        <v>46158.95833333334</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" t="n">
+        <v>0</v>
+      </c>
+      <c r="I273" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" t="n">
+        <v>0</v>
+      </c>
+      <c r="K273" t="n">
+        <v>0</v>
+      </c>
+      <c r="L273" t="n">
+        <v>0</v>
+      </c>
+      <c r="M273" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N273" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P273" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>0</v>
+      </c>
+      <c r="R273" t="n">
+        <v>0</v>
+      </c>
+      <c r="S273" t="n">
+        <v>0</v>
+      </c>
+      <c r="T273" t="n">
+        <v>0</v>
+      </c>
+      <c r="U273" t="n">
+        <v>0</v>
+      </c>
+      <c r="V273" t="n">
+        <v>0</v>
+      </c>
+      <c r="W273" t="n">
+        <v>0</v>
+      </c>
+      <c r="X273" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ273" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA273" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB273" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC273" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD273" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE273" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF273" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG273" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH273" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI273" s="3" t="n">
         <v>46158.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-05-16.xlsx
+++ b/jogos_2026-05-16.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.98</v>
+        <v>3.23</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R64" t="n">
-        <v>3.78</v>
+        <v>2.11</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.37</v>
+        <v>1.72</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="R68" t="n">
-        <v>2.11</v>
+        <v>4.6</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="R69" t="n">
-        <v>3.43</v>
+        <v>3.78</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.23</v>
+        <v>1.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="R71" t="n">
-        <v>2.11</v>
+        <v>6.19</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.5</v>
+        <v>3.37</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.68</v>
+        <v>3.3</v>
       </c>
       <c r="R73" t="n">
-        <v>6.19</v>
+        <v>2.11</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.72</v>
+        <v>1.15</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.74</v>
+        <v>5.5</v>
       </c>
       <c r="R75" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.82</v>
+        <v>1.28</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.1</v>
+        <v>7.13</v>
       </c>
       <c r="R79" t="n">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="Q80" t="n">
-        <v>7.13</v>
+        <v>5.95</v>
       </c>
       <c r="R80" t="n">
-        <v>11</v>
+        <v>6.36</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16367,10 +16367,10 @@
         <v>2.77</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.49</v>
+        <v>4.41</v>
       </c>
       <c r="R81" t="n">
-        <v>2.72</v>
+        <v>2.34</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.45</v>
+        <v>2.77</v>
       </c>
       <c r="Q82" t="n">
-        <v>5.95</v>
+        <v>3.49</v>
       </c>
       <c r="R82" t="n">
-        <v>6.36</v>
+        <v>2.72</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.41</v>
+        <v>4.31</v>
       </c>
       <c r="R83" t="n">
-        <v>2.34</v>
+        <v>2.09</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.57</v>
+        <v>2.82</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="R84" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>3.7</v>
+        <v>2.57</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.52</v>
+        <v>4.22</v>
       </c>
       <c r="R85" t="n">
-        <v>1.91</v>
+        <v>2.57</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.31</v>
+        <v>4.52</v>
       </c>
       <c r="R87" t="n">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.87</v>
+        <v>3.76</v>
       </c>
       <c r="R88" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="Q92" t="n">
-        <v>5.06</v>
+        <v>3.87</v>
       </c>
       <c r="R92" t="n">
-        <v>6.61</v>
+        <v>3.92</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19328,124 +19328,124 @@
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T96" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U96" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V96" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AH96" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI96" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AJ96" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK96" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL96" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM96" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AN96" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO96" t="n">
         <v>0</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR96" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AS96" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AT96" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AU96" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AV96" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW96" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX96" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY96" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ96" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BA96" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BB96" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD96" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE96" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF96" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.78</v>
+        <v>1.43</v>
       </c>
       <c r="Q98" t="n">
-        <v>4.13</v>
+        <v>5.06</v>
       </c>
       <c r="R98" t="n">
-        <v>4.13</v>
+        <v>6.61</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19919,124 +19919,124 @@
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V99" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD99" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG99" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AH99" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI99" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AJ99" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK99" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL99" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM99" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AN99" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO99" t="n">
         <v>0</v>
       </c>
       <c r="AP99" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR99" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS99" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AU99" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AV99" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW99" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX99" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY99" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ99" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA99" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BB99" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC99" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD99" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE99" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF99" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG99" t="n">
         <v>0</v>
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.98</v>
+        <v>2</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R108" t="n">
-        <v>2.21</v>
+        <v>3.3</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.79</v>
+        <v>6.15</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="R127" t="n">
-        <v>3.7</v>
+        <v>1.46</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="Q129" t="n">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="R129" t="n">
-        <v>9.050000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>6.15</v>
+        <v>1.25</v>
       </c>
       <c r="Q130" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="R130" t="n">
-        <v>1.46</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.14</v>
+        <v>3.16</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="R140" t="n">
-        <v>3.38</v>
+        <v>2.07</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,22 +28136,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>2.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="R146" t="n">
-        <v>3.64</v>
+        <v>1.69</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>4.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q148" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="R148" t="n">
-        <v>1.69</v>
+        <v>3.38</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.75</v>
+        <v>2.07</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R150" t="n">
-        <v>2.65</v>
+        <v>3.64</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,22 +30106,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>2.46</v>
+        <v>1.75</v>
       </c>
       <c r="Q154" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="R154" t="n">
-        <v>3.11</v>
+        <v>4.09</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q159" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>2.54</v>
+        <v>1.8</v>
       </c>
       <c r="Q160" t="n">
-        <v>3.01</v>
+        <v>4</v>
       </c>
       <c r="R160" t="n">
-        <v>3.17</v>
+        <v>4.26</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32470,22 +32470,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q163" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q167" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33351,10 +33351,10 @@
         <v>0</v>
       </c>
       <c r="AE167" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF167" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG167" t="n">
         <v>0</v>
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33745,10 +33745,10 @@
         <v>0</v>
       </c>
       <c r="AE169" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF169" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG169" t="n">
         <v>0</v>
@@ -33849,22 +33849,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,22 +34046,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35079,13 +35079,13 @@
         </is>
       </c>
       <c r="P176" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q176" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -35228,22 +35228,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q177" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q178" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q179" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="Q180" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36213,22 +36213,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>1.86</v>
+        <v>2.75</v>
       </c>
       <c r="Q182" t="n">
-        <v>4.04</v>
+        <v>3.1</v>
       </c>
       <c r="R182" t="n">
-        <v>3.82</v>
+        <v>2.65</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36312,10 +36312,10 @@
         <v>0</v>
       </c>
       <c r="AG182" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH182" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI182" t="n">
         <v>0</v>
@@ -36410,22 +36410,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>2.75</v>
+        <v>1.86</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.1</v>
+        <v>4.04</v>
       </c>
       <c r="R183" t="n">
-        <v>2.65</v>
+        <v>3.82</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36509,10 +36509,10 @@
         <v>0</v>
       </c>
       <c r="AG183" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH183" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37789,7 +37789,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q196" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF196" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q198" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39610,13 +39610,13 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q199" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -39655,10 +39655,10 @@
         <v>0</v>
       </c>
       <c r="AE199" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF199" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG199" t="n">
         <v>0</v>
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q203" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q210" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R210" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41926,7 +41926,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,7 +42123,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,22 +42517,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,7 +42911,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,22 +43305,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,22 +43502,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,22 +44290,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44881,22 +44881,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -45088,12 +45088,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -45285,12 +45285,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45472,22 +45472,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45520,13 +45520,13 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q229" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -45565,10 +45565,10 @@
         <v>0</v>
       </c>
       <c r="AE229" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF229" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG229" t="n">
         <v>0</v>
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,22 +47048,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,13 +47096,13 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q237" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R237" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="S237" t="n">
         <v>0</v>
@@ -47141,10 +47141,10 @@
         <v>0</v>
       </c>
       <c r="AE237" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF237" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG237" t="n">
         <v>0</v>
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47293,13 +47293,13 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q238" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="R238" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S238" t="n">
         <v>0</v>
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47836,7 +47836,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,22 +48033,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48230,7 +48230,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51185,7 +51185,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51579,7 +51579,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52367,22 +52367,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52415,13 +52415,13 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q264" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S264" t="n">
         <v>0</v>
@@ -52564,7 +52564,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -52574,12 +52574,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,7 +52958,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G271" t="n">

--- a/jogos_2026-05-16.xlsx
+++ b/jogos_2026-05-16.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.67</v>
+        <v>1.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.46</v>
+        <v>3.76</v>
       </c>
       <c r="R20" t="n">
-        <v>1.84</v>
+        <v>6.81</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.36</v>
+        <v>4.67</v>
       </c>
       <c r="Q21" t="n">
         <v>3.46</v>
       </c>
       <c r="R21" t="n">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.69</v>
+        <v>2.12</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.08</v>
+        <v>3.5</v>
       </c>
       <c r="R53" t="n">
-        <v>4.75</v>
+        <v>3.12</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.67</v>
+        <v>4.08</v>
       </c>
       <c r="R61" t="n">
-        <v>3.47</v>
+        <v>4.75</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.23</v>
+        <v>1.5</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.78</v>
+        <v>3.68</v>
       </c>
       <c r="R67" t="n">
-        <v>3.43</v>
+        <v>6.19</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.72</v>
+        <v>2.23</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.74</v>
+        <v>2.78</v>
       </c>
       <c r="R68" t="n">
-        <v>4.6</v>
+        <v>3.43</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.68</v>
+        <v>5.5</v>
       </c>
       <c r="R71" t="n">
-        <v>6.19</v>
+        <v>13</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.15</v>
+        <v>3.23</v>
       </c>
       <c r="Q75" t="n">
-        <v>5.5</v>
+        <v>3.35</v>
       </c>
       <c r="R75" t="n">
-        <v>13</v>
+        <v>2.11</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.45</v>
+        <v>2.82</v>
       </c>
       <c r="Q80" t="n">
-        <v>5.95</v>
+        <v>4.1</v>
       </c>
       <c r="R80" t="n">
-        <v>6.36</v>
+        <v>2.4</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.77</v>
+        <v>1.45</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.41</v>
+        <v>5.95</v>
       </c>
       <c r="R81" t="n">
-        <v>2.34</v>
+        <v>6.36</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16564,10 +16564,10 @@
         <v>2.77</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.49</v>
+        <v>4.41</v>
       </c>
       <c r="R82" t="n">
-        <v>2.72</v>
+        <v>2.34</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.31</v>
+        <v>3.49</v>
       </c>
       <c r="R83" t="n">
-        <v>2.09</v>
+        <v>2.72</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.82</v>
+        <v>3.48</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.1</v>
+        <v>4.19</v>
       </c>
       <c r="R84" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.57</v>
+        <v>3.28</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.22</v>
+        <v>4.31</v>
       </c>
       <c r="R85" t="n">
-        <v>2.57</v>
+        <v>2.09</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.19</v>
+        <v>4.52</v>
       </c>
       <c r="R86" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.7</v>
+        <v>2.57</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.52</v>
+        <v>4.22</v>
       </c>
       <c r="R87" t="n">
-        <v>1.91</v>
+        <v>2.57</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.76</v>
+        <v>3.87</v>
       </c>
       <c r="R88" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2</v>
+        <v>1.32</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.87</v>
+        <v>5.73</v>
       </c>
       <c r="R91" t="n">
-        <v>3.46</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.88</v>
+        <v>1.43</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.87</v>
+        <v>5.06</v>
       </c>
       <c r="R92" t="n">
-        <v>3.92</v>
+        <v>6.61</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>5.73</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,133 +19713,133 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>6.61</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V98" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG98" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AH98" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI98" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK98" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL98" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM98" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AN98" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO98" t="n">
         <v>0</v>
       </c>
       <c r="AP98" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR98" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS98" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AU98" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AV98" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW98" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX98" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY98" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ98" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA98" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BB98" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD98" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE98" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF98" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19919,124 +19919,124 @@
         <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI99" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AJ99" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK99" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL99" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM99" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AN99" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO99" t="n">
         <v>0</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR99" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AS99" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AT99" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AU99" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AV99" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW99" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX99" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY99" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ99" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BA99" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BB99" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC99" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE99" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF99" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.96</v>
+        <v>3.06</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.63</v>
+        <v>3.22</v>
       </c>
       <c r="R104" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.22</v>
+        <v>3.63</v>
       </c>
       <c r="R105" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R108" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R109" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>6.15</v>
+        <v>1.79</v>
       </c>
       <c r="Q127" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="R127" t="n">
-        <v>1.46</v>
+        <v>3.7</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>3.91</v>
+        <v>6.15</v>
       </c>
       <c r="Q128" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="R128" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25674,10 +25674,10 @@
         <v>0</v>
       </c>
       <c r="AG128" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH128" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AI128" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="R129" t="n">
-        <v>3.7</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1.25</v>
+        <v>3.91</v>
       </c>
       <c r="Q130" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="R130" t="n">
-        <v>9.050000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26068,10 +26068,10 @@
         <v>0</v>
       </c>
       <c r="AG130" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH130" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AI130" t="n">
         <v>0</v>
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>3.16</v>
+        <v>2.75</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="R140" t="n">
-        <v>2.07</v>
+        <v>2.65</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,22 +28727,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>4.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q146" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="R146" t="n">
-        <v>1.69</v>
+        <v>3.38</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.14</v>
+        <v>2.46</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R148" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29712,22 +29712,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="R150" t="n">
-        <v>3.64</v>
+        <v>4.09</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>2.75</v>
+        <v>4.08</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="R151" t="n">
-        <v>2.65</v>
+        <v>1.69</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,22 +30303,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q152" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30697,22 +30697,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30745,13 +30745,13 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2.54</v>
+        <v>2.12</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.01</v>
+        <v>3.62</v>
       </c>
       <c r="R162" t="n">
-        <v>3.17</v>
+        <v>3.41</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32480,12 +32480,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -32518,13 +32518,13 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>2.12</v>
+        <v>2.54</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.62</v>
+        <v>3.01</v>
       </c>
       <c r="R163" t="n">
-        <v>3.41</v>
+        <v>3.17</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33154,10 +33154,10 @@
         <v>0</v>
       </c>
       <c r="AE166" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF166" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG166" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33745,10 +33745,10 @@
         <v>0</v>
       </c>
       <c r="AE169" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF169" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG169" t="n">
         <v>0</v>
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,22 +34243,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q172" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="R172" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,22 +34440,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,22 +34637,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -35031,22 +35031,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35276,13 +35276,13 @@
         </is>
       </c>
       <c r="P177" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35473,13 +35473,13 @@
         </is>
       </c>
       <c r="P178" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q178" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35670,13 +35670,13 @@
         </is>
       </c>
       <c r="P179" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q179" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -35867,13 +35867,13 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="Q180" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -36026,12 +36026,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -36064,13 +36064,13 @@
         </is>
       </c>
       <c r="P181" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37986,7 +37986,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,10 +38670,10 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF194" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q196" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q197" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q198" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39562,7 +39562,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -39572,12 +39572,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -39610,13 +39610,13 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>1.35</v>
+        <v>2.03</v>
       </c>
       <c r="Q199" t="n">
-        <v>4.7</v>
+        <v>3.48</v>
       </c>
       <c r="R199" t="n">
-        <v>8.5</v>
+        <v>3.83</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -39655,10 +39655,10 @@
         <v>0</v>
       </c>
       <c r="AE199" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF199" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG199" t="n">
         <v>0</v>
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q206" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R206" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q210" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -42123,22 +42123,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q212" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF212" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,22 +42517,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42911,22 +42911,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -43108,22 +43108,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43305,22 +43305,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43502,22 +43502,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -43699,7 +43699,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -43709,12 +43709,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -43896,7 +43896,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -43906,12 +43906,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -44093,7 +44093,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -44103,12 +44103,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -44300,12 +44300,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -44487,7 +44487,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -44694,12 +44694,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -44881,7 +44881,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -44891,12 +44891,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -45078,22 +45078,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -45275,22 +45275,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -45323,13 +45323,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q228" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="R228" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -45472,7 +45472,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -45482,12 +45482,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -45679,12 +45679,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -45876,12 +45876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -46073,12 +46073,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -46260,7 +46260,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -46270,12 +46270,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -46457,7 +46457,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -46467,12 +46467,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -46654,7 +46654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -46664,12 +46664,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -46851,7 +46851,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -46861,12 +46861,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -47048,22 +47048,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -47096,13 +47096,13 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q237" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="S237" t="n">
         <v>0</v>
@@ -47141,10 +47141,10 @@
         <v>0</v>
       </c>
       <c r="AE237" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF237" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG237" t="n">
         <v>0</v>
@@ -47245,22 +47245,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -47293,13 +47293,13 @@
         </is>
       </c>
       <c r="P238" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q238" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="R238" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="S238" t="n">
         <v>0</v>
@@ -47442,7 +47442,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -47452,12 +47452,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -47649,12 +47649,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -47846,12 +47846,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -48033,7 +48033,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -48043,12 +48043,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -48240,12 +48240,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -48427,7 +48427,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -48437,12 +48437,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -48624,7 +48624,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -48634,12 +48634,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -48821,7 +48821,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -48831,12 +48831,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -49018,7 +49018,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -49028,12 +49028,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -49225,12 +49225,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -49422,12 +49422,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -49609,7 +49609,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -49619,12 +49619,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -49816,12 +49816,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -50003,7 +50003,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -50013,12 +50013,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -50200,7 +50200,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -50210,12 +50210,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -50397,7 +50397,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -50594,7 +50594,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -50604,12 +50604,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -50801,12 +50801,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -50988,7 +50988,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -50998,12 +50998,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -51195,12 +51195,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -51382,7 +51382,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -51392,12 +51392,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -51589,12 +51589,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -51776,7 +51776,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -51786,12 +51786,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Mohammedan</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -51983,12 +51983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Mohammedan</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -52180,12 +52180,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -52377,12 +52377,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -52761,7 +52761,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -52771,12 +52771,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -52958,7 +52958,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -52968,12 +52968,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -53559,12 +53559,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -53756,12 +53756,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G271" t="n">

--- a/jogos_2026-05-16.xlsx
+++ b/jogos_2026-05-16.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.36</v>
+        <v>2.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.46</v>
+        <v>3.06</v>
       </c>
       <c r="R15" t="n">
-        <v>2.18</v>
+        <v>2.69</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.76</v>
+        <v>3.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.56</v>
+        <v>3.46</v>
       </c>
       <c r="R19" t="n">
-        <v>5.07</v>
+        <v>2.18</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.43</v>
+        <v>1.58</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.06</v>
+        <v>3.76</v>
       </c>
       <c r="R25" t="n">
-        <v>2.69</v>
+        <v>6.81</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.69</v>
+        <v>2.08</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.08</v>
+        <v>3.67</v>
       </c>
       <c r="R61" t="n">
-        <v>4.75</v>
+        <v>3.47</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.5</v>
+        <v>2.23</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.68</v>
+        <v>2.78</v>
       </c>
       <c r="R67" t="n">
-        <v>6.19</v>
+        <v>3.43</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.23</v>
+        <v>1.15</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.78</v>
+        <v>5.5</v>
       </c>
       <c r="R68" t="n">
-        <v>3.43</v>
+        <v>13</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.15</v>
+        <v>2.62</v>
       </c>
       <c r="Q71" t="n">
-        <v>5.5</v>
+        <v>2.93</v>
       </c>
       <c r="R71" t="n">
-        <v>13</v>
+        <v>2.58</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.72</v>
+        <v>3.23</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.74</v>
+        <v>3.35</v>
       </c>
       <c r="R72" t="n">
-        <v>4.6</v>
+        <v>2.11</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.23</v>
+        <v>1.5</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="R75" t="n">
-        <v>2.11</v>
+        <v>6.19</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.37</v>
+        <v>1.89</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="R76" t="n">
-        <v>2.11</v>
+        <v>4.29</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.28</v>
+        <v>3.48</v>
       </c>
       <c r="Q79" t="n">
-        <v>7.13</v>
+        <v>4.19</v>
       </c>
       <c r="R79" t="n">
-        <v>11</v>
+        <v>2.05</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.82</v>
+        <v>3.7</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.1</v>
+        <v>4.52</v>
       </c>
       <c r="R80" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="Q81" t="n">
-        <v>5.95</v>
+        <v>7.13</v>
       </c>
       <c r="R81" t="n">
-        <v>6.36</v>
+        <v>11</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.41</v>
+        <v>4.31</v>
       </c>
       <c r="R82" t="n">
-        <v>2.34</v>
+        <v>2.09</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16761,10 +16761,10 @@
         <v>2.77</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.49</v>
+        <v>4.41</v>
       </c>
       <c r="R83" t="n">
-        <v>2.72</v>
+        <v>2.34</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>3.48</v>
+        <v>1.45</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.19</v>
+        <v>5.95</v>
       </c>
       <c r="R84" t="n">
-        <v>2.05</v>
+        <v>6.36</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.31</v>
+        <v>3.49</v>
       </c>
       <c r="R85" t="n">
-        <v>2.09</v>
+        <v>2.72</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>3.7</v>
+        <v>2.82</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.52</v>
+        <v>4.1</v>
       </c>
       <c r="R86" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.88</v>
+        <v>3.44</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.87</v>
+        <v>3.82</v>
       </c>
       <c r="R88" t="n">
-        <v>3.92</v>
+        <v>1.92</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.43</v>
+        <v>1.78</v>
       </c>
       <c r="Q92" t="n">
-        <v>5.06</v>
+        <v>4.13</v>
       </c>
       <c r="R92" t="n">
-        <v>6.61</v>
+        <v>4.13</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18976,10 +18976,10 @@
         <v>0</v>
       </c>
       <c r="AG94" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>6.61</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
